--- a/kyorindo-cx/04_references/競合DXベンチマーク_20260423.xlsx
+++ b/kyorindo-cx/04_references/競合DXベンチマーク_20260423.xlsx
@@ -689,7 +689,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I78"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -697,10 +697,11 @@
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="36" customWidth="1" min="7" max="7"/>
-    <col width="32" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="32" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="30" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -743,15 +744,20 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
+          <t>実装時期</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
           <t>主な導入目的</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>成果・実績</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>ツルハHD比較</t>
         </is>
@@ -788,17 +794,22 @@
           <t>ダイナミックプライシング（564商品）</t>
         </is>
       </c>
-      <c r="G3" s="7" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>2023年頃</t>
+        </is>
+      </c>
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>粗利改善・在庫最適化</t>
         </is>
       </c>
-      <c r="H3" s="7" t="inlineStr">
+      <c r="I3" s="7" t="inlineStr">
         <is>
           <t>対象商品粗利+30%以上</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="J3" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -819,17 +830,22 @@
           <t>AI売上予測「SalesSensor」</t>
         </is>
       </c>
-      <c r="G4" s="7" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>2025年度</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>需要予測精度向上・販売計画最適化</t>
         </is>
       </c>
-      <c r="H4" s="7" t="inlineStr">
+      <c r="I4" s="7" t="inlineStr">
         <is>
           <t>2025年度導入</t>
         </is>
       </c>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="J4" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -850,17 +866,22 @@
           <t>カスタマーAI（NEL）</t>
         </is>
       </c>
-      <c r="G5" s="7" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>2024年</t>
+        </is>
+      </c>
+      <c r="H5" s="7" t="inlineStr">
         <is>
           <t>顧客対応工数削減・CS品質向上</t>
         </is>
       </c>
-      <c r="H5" s="7" t="inlineStr">
+      <c r="I5" s="7" t="inlineStr">
         <is>
           <t>工数90%削減</t>
         </is>
       </c>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="J5" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -881,17 +902,22 @@
           <t>Treasure Data CDP</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>2022年頃</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>医療・健康・POSデータ統合・MAツール実装</t>
         </is>
       </c>
-      <c r="H6" s="7" t="inlineStr">
+      <c r="I6" s="7" t="inlineStr">
         <is>
           <t>データ統合完了・MAツール実装済み</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="J6" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -912,17 +938,22 @@
           <t>混雑チェックアプリ</t>
         </is>
       </c>
-      <c r="G7" s="7" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
         <is>
           <t>来店体験向上・混雑回避</t>
         </is>
       </c>
-      <c r="H7" s="7" t="inlineStr">
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I7" s="10" t="inlineStr">
+      <c r="J7" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -943,17 +974,22 @@
           <t>モバイルTカード</t>
         </is>
       </c>
-      <c r="G8" s="7" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>デジタル会員証化・レジ待ち削減</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I8" s="10" t="inlineStr">
+      <c r="J8" s="10" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -974,17 +1010,22 @@
           <t>1to1マーケティング（True Data）</t>
         </is>
       </c>
-      <c r="G9" s="7" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
         <is>
           <t>購買行動に基づくパーソナライズ提案</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1005,17 +1046,22 @@
           <t>オンライン服薬指導</t>
         </is>
       </c>
-      <c r="G10" s="7" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>患者利便性向上・遠隔医療対応</t>
         </is>
       </c>
-      <c r="H10" s="7" t="inlineStr">
+      <c r="I10" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I10" s="10" t="inlineStr">
+      <c r="J10" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1036,17 +1082,22 @@
           <t>デジタルサイネージ</t>
         </is>
       </c>
-      <c r="G11" s="7" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>2023年（1,600店）</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
         <is>
           <t>店内広告収益化・購買促進</t>
         </is>
       </c>
-      <c r="H11" s="7" t="inlineStr">
+      <c r="I11" s="7" t="inlineStr">
         <is>
           <t>1,600店導入済み</t>
         </is>
       </c>
-      <c r="I11" s="10" t="inlineStr">
+      <c r="J11" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1067,17 +1118,22 @@
           <t>業務端末リプレイス（2026年）</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>2026年予定</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>現場業務効率化・デジタル化推進</t>
         </is>
       </c>
-      <c r="H12" s="7" t="inlineStr">
+      <c r="I12" s="7" t="inlineStr">
         <is>
           <t>2026年完了予定</t>
         </is>
       </c>
-      <c r="I12" s="10" t="inlineStr">
+      <c r="J12" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1114,17 +1170,22 @@
           <t>公式アプリ（ポイントカード・クーポン・チラシ）</t>
         </is>
       </c>
-      <c r="G13" s="7" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
         <is>
           <t>顧客接点デジタル化・来店促進</t>
         </is>
       </c>
-      <c r="H13" s="7" t="inlineStr">
+      <c r="I13" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I13" s="10" t="inlineStr">
+      <c r="J13" s="10" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -1145,17 +1206,22 @@
           <t>処方箋事前送信（アプリ経由）</t>
         </is>
       </c>
-      <c r="G14" s="7" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
         <is>
           <t>調剤待ち時間削減・患者利便性向上</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr">
+      <c r="I14" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I14" s="10" t="inlineStr">
+      <c r="J14" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1192,17 +1258,22 @@
           <t>品揃え最適化AI（エクサウィザーズ共同開発）</t>
         </is>
       </c>
-      <c r="G15" s="7" t="inlineStr">
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
         <is>
           <t>在庫最適化・品揃え精度向上</t>
         </is>
       </c>
-      <c r="H15" s="7" t="inlineStr">
+      <c r="I15" s="7" t="inlineStr">
         <is>
           <t>実装済み（詳細非公開）</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1223,17 +1294,22 @@
           <t>薬剤師アシスタントAI</t>
         </is>
       </c>
-      <c r="G16" s="7" t="inlineStr">
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>2026年4月（本番化）</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
         <is>
           <t>薬剤師の問い合わせ対応効率化</t>
         </is>
       </c>
-      <c r="H16" s="7" t="inlineStr">
+      <c r="I16" s="7" t="inlineStr">
         <is>
           <t>200店舗展開・2026年4月本番化</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1254,17 +1330,22 @@
           <t>データレイクハウス（AWS）</t>
         </is>
       </c>
-      <c r="G17" s="7" t="inlineStr">
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>構築中</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
         <is>
           <t>社内分散データ統合・データドリブン経営</t>
         </is>
       </c>
-      <c r="H17" s="7" t="inlineStr">
+      <c r="I17" s="7" t="inlineStr">
         <is>
           <t>構築中</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1285,17 +1366,22 @@
           <t>スギ薬局アプリ</t>
         </is>
       </c>
-      <c r="G18" s="7" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
         <is>
           <t>既存顧客の深化・LTV向上</t>
         </is>
       </c>
-      <c r="H18" s="7" t="inlineStr">
+      <c r="I18" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I18" s="10" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -1316,17 +1402,22 @@
           <t>アバター遠隔接客</t>
         </is>
       </c>
-      <c r="G19" s="7" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>2022年頃</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
         <is>
           <t>問い合わせ対応効率化・省人化</t>
         </is>
       </c>
-      <c r="H19" s="7" t="inlineStr">
+      <c r="I19" s="7" t="inlineStr">
         <is>
           <t>対応時間1/4に短縮</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="J19" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1347,17 +1438,22 @@
           <t>生活習慣病リスクレポート</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
         <is>
           <t>ヘルスケア提案強化・健康管理サービス</t>
         </is>
       </c>
-      <c r="H20" s="7" t="inlineStr">
+      <c r="I20" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1378,17 +1474,22 @@
           <t>スギスマホでお薬</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
         <is>
           <t>処方箋デジタル化・待ち時間削減</t>
         </is>
       </c>
-      <c r="H21" s="7" t="inlineStr">
+      <c r="I21" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="J21" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1409,17 +1510,22 @@
           <t>リテールメディア「お茶の間」戦略</t>
         </is>
       </c>
-      <c r="G22" s="7" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
         <is>
           <t>購買データ活用でメーカー向け広告収益化</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
+      <c r="I22" s="7" t="inlineStr">
         <is>
           <t>購買率前年比144%</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="J22" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1440,17 +1546,22 @@
           <t>生成AI QAボット（年末調整）</t>
         </is>
       </c>
-      <c r="G23" s="7" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>2024年頃</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
         <is>
           <t>問い合わせ対応工数削減・ナレッジ共有</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
+      <c r="I23" s="7" t="inlineStr">
         <is>
           <t>1ヶ月で構築・200店展開</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="J23" s="10" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -1487,17 +1598,22 @@
           <t>商品DNA（意識スコアタグ付け）</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
         <is>
           <t>購買データ活用・PB商品開発精度向上</t>
         </is>
       </c>
-      <c r="H24" s="7" t="inlineStr">
+      <c r="I24" s="7" t="inlineStr">
         <is>
           <t>新規顧客9割のPB開発実現</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="J24" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1518,17 +1634,22 @@
           <t>リアル×デジタル統合プラットフォーム</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
         <is>
           <t>顧客データ統合・接点最大化</t>
         </is>
       </c>
-      <c r="H25" s="7" t="inlineStr">
+      <c r="I25" s="7" t="inlineStr">
         <is>
           <t>会員2,342万人・接点1億5,000万超</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1549,17 +1670,22 @@
           <t>ARメイクシミュレーター「Be Makeup+」</t>
         </is>
       </c>
-      <c r="G26" s="7" t="inlineStr">
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
         <is>
           <t>購買前のデジタル体験提供・EC誘導</t>
         </is>
       </c>
-      <c r="H26" s="7" t="inlineStr">
+      <c r="I26" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="J26" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1580,17 +1706,22 @@
           <t>肌診断「Be Skincare+」・髪診断「Be Haircare+」</t>
         </is>
       </c>
-      <c r="G27" s="7" t="inlineStr">
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
         <is>
           <t>スキンケア・ヘアケア提案強化</t>
         </is>
       </c>
-      <c r="H27" s="7" t="inlineStr">
+      <c r="I27" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1611,17 +1742,22 @@
           <t>店舗発送型EC「マツキヨコクミンQ」</t>
         </is>
       </c>
-      <c r="G28" s="7" t="inlineStr">
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H28" s="7" t="inlineStr">
         <is>
           <t>即日配送で利便性向上・EC収益拡大</t>
         </is>
       </c>
-      <c r="H28" s="7" t="inlineStr">
+      <c r="I28" s="7" t="inlineStr">
         <is>
           <t>21都道府県展開</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="J28" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1642,17 +1778,22 @@
           <t>処方箋事前送信・電子お薬手帳（マツキヨコクミンMe）</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr">
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
         <is>
           <t>調剤業務デジタル化・患者利便性向上</t>
         </is>
       </c>
-      <c r="H29" s="7" t="inlineStr">
+      <c r="I29" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="J29" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1673,17 +1814,22 @@
           <t>Matsukiyo Ads（メーカー向け広告プラットフォーム）</t>
         </is>
       </c>
-      <c r="G30" s="7" t="inlineStr">
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
         <is>
           <t>ファーストパーティデータ活用での広告収益化</t>
         </is>
       </c>
-      <c r="H30" s="7" t="inlineStr">
+      <c r="I30" s="7" t="inlineStr">
         <is>
           <t>購買データ×Google広告で運用</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="J30" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -1720,17 +1866,22 @@
           <t>AIチャットボット「WisTalk」</t>
         </is>
       </c>
-      <c r="G31" s="7" t="inlineStr">
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
         <is>
           <t>社内問い合わせ対応自動化・業務効率化</t>
         </is>
       </c>
-      <c r="H31" s="7" t="inlineStr">
+      <c r="I31" s="7" t="inlineStr">
         <is>
           <t>業務負荷75%削減</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="J31" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1751,17 +1902,22 @@
           <t>クラウドPOS（TMN）</t>
         </is>
       </c>
-      <c r="G32" s="7" t="inlineStr">
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
         <is>
           <t>販売データのリアルタイム活用・分析</t>
         </is>
       </c>
-      <c r="H32" s="7" t="inlineStr">
+      <c r="I32" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I32" s="10" t="inlineStr">
+      <c r="J32" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1782,17 +1938,22 @@
           <t>SuperStream-NX Cloud</t>
         </is>
       </c>
-      <c r="G33" s="7" t="inlineStr">
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
         <is>
           <t>月次決算早期化・財務DXの推進</t>
         </is>
       </c>
-      <c r="H33" s="7" t="inlineStr">
+      <c r="I33" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="J33" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1813,17 +1974,22 @@
           <t>公式アプリ（Aocaポイント・処方箋送信・電子お薬手帳）</t>
         </is>
       </c>
-      <c r="G34" s="7" t="inlineStr">
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
         <is>
           <t>顧客接点デジタル化・利便性向上</t>
         </is>
       </c>
-      <c r="H34" s="7" t="inlineStr">
+      <c r="I34" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="J34" s="10" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -1844,17 +2010,22 @@
           <t>処方箋スマホ送信・電子お薬手帳（アプリ内）</t>
         </is>
       </c>
-      <c r="G35" s="7" t="inlineStr">
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
         <is>
           <t>調剤待ち時間削減・ペーパーレス化</t>
         </is>
       </c>
-      <c r="H35" s="7" t="inlineStr">
+      <c r="I35" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="J35" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1891,17 +2062,22 @@
           <t>（DX情報確認できていない）</t>
         </is>
       </c>
-      <c r="G36" s="7" t="inlineStr">
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
         <is>
           <t>低価格食品訴求型。DXより価格競争力で差別化</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr">
+      <c r="I36" s="7" t="inlineStr">
         <is>
           <t>確認できていない</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="J36" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1938,17 +2114,22 @@
           <t>POS×棚割り連動システム</t>
         </is>
       </c>
-      <c r="G37" s="7" t="inlineStr">
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
         <is>
           <t>陳列最適化・フェース数管理の徹底</t>
         </is>
       </c>
-      <c r="H37" s="7" t="inlineStr">
+      <c r="I37" s="7" t="inlineStr">
         <is>
           <t>全店一元管理実装済み</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="J37" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -1969,17 +2150,22 @@
           <t>本部一元管理型自動発注システム</t>
         </is>
       </c>
-      <c r="G38" s="7" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
         <is>
           <t>在庫最適化・人的作業削減</t>
         </is>
       </c>
-      <c r="H38" s="7" t="inlineStr">
+      <c r="I38" s="7" t="inlineStr">
         <is>
           <t>全店展開済み</t>
         </is>
       </c>
-      <c r="I38" s="10" t="inlineStr">
+      <c r="J38" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2000,17 +2186,22 @@
           <t>アプリ内オンラインストア（アプリ限定商品・クーポン）</t>
         </is>
       </c>
-      <c r="G39" s="7" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
         <is>
           <t>顧客接点拡大・EC収益化</t>
         </is>
       </c>
-      <c r="H39" s="7" t="inlineStr">
+      <c r="I39" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="J39" s="10" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -2031,17 +2222,22 @@
           <t>本部×店舗の役割分担明確化</t>
         </is>
       </c>
-      <c r="G40" s="7" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
         <is>
           <t>オペレーション効率化・店舗負荷軽減</t>
         </is>
       </c>
-      <c r="H40" s="7" t="inlineStr">
+      <c r="I40" s="7" t="inlineStr">
         <is>
           <t>全社展開済み</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="J40" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2078,17 +2274,22 @@
           <t>AI FAQシステム（ユーザーローカル）</t>
         </is>
       </c>
-      <c r="G41" s="7" t="inlineStr">
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
         <is>
           <t>カスタマーサポート効率化・問い合わせ自動応答</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
+      <c r="I41" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="J41" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2109,17 +2310,22 @@
           <t>AIカメラ実証実験（Ultimatrust）</t>
         </is>
       </c>
-      <c r="G42" s="7" t="inlineStr">
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
         <is>
           <t>来客動態分析・店舗改善</t>
         </is>
       </c>
-      <c r="H42" s="7" t="inlineStr">
+      <c r="I42" s="7" t="inlineStr">
         <is>
           <t>実証実験中</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="J42" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2140,17 +2346,22 @@
           <t>Salesforce Service Cloud＋Experience Cloud</t>
         </is>
       </c>
-      <c r="G43" s="7" t="inlineStr">
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
         <is>
           <t>EC・店舗コミュニケーション一元管理</t>
         </is>
       </c>
-      <c r="H43" s="7" t="inlineStr">
+      <c r="I43" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="J43" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2171,17 +2382,22 @@
           <t>Shopify Plus ECサイトリニューアル</t>
         </is>
       </c>
-      <c r="G44" s="7" t="inlineStr">
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
         <is>
           <t>EC体験向上・売上拡大</t>
         </is>
       </c>
-      <c r="H44" s="7" t="inlineStr">
+      <c r="I44" s="7" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="J44" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2202,17 +2418,22 @@
           <t>Criteoリテールメディア</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr">
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
         <is>
           <t>ファーストパーティデータ活用でメーカー向け広告収益化</t>
         </is>
       </c>
-      <c r="H45" s="7" t="inlineStr">
+      <c r="I45" s="7" t="inlineStr">
         <is>
           <t>業界先駆け・先行優位を確立</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="J45" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -2233,17 +2454,22 @@
           <t>トクスルビジョン（デジタルサイネージ）</t>
         </is>
       </c>
-      <c r="G46" s="7" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>2025年3月（全1,000店）</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
         <is>
           <t>店内広告のデジタル化・広告収益化</t>
         </is>
       </c>
-      <c r="H46" s="7" t="inlineStr">
+      <c r="I46" s="7" t="inlineStr">
         <is>
           <t>全1,000店・2025年3月導入完了</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="J46" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2280,17 +2506,22 @@
           <t>（DX情報確認できていない）</t>
         </is>
       </c>
-      <c r="G47" s="7" t="inlineStr">
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
         <is>
           <t>大型郊外店型。静岡への進出は現時点で未確認</t>
         </is>
       </c>
-      <c r="H47" s="7" t="inlineStr">
+      <c r="I47" s="7" t="inlineStr">
         <is>
           <t>確認できていない</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="J47" s="10" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2327,17 +2558,22 @@
           <t>AIワーク・MaIボード</t>
         </is>
       </c>
-      <c r="G48" s="18" t="inlineStr">
+      <c r="G48" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
         <is>
           <t>店舗業務効率化・AI活用推進</t>
         </is>
       </c>
-      <c r="H48" s="18" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>約350店導入</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="J48" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2358,17 +2594,22 @@
           <t>生成AI推進（グループ1,000人トライアル）</t>
         </is>
       </c>
-      <c r="G49" s="18" t="inlineStr">
+      <c r="G49" s="16" t="inlineStr">
+        <is>
+          <t>2023年頃</t>
+        </is>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
         <is>
           <t>生成AIスキル育成・業務効率化</t>
         </is>
       </c>
-      <c r="H49" s="18" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>グループ全体でトライアル中</t>
         </is>
       </c>
-      <c r="I49" s="19" t="inlineStr">
+      <c r="J49" s="19" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
@@ -2389,17 +2630,22 @@
           <t>イオングループデータ統合基盤</t>
         </is>
       </c>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="G50" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
         <is>
           <t>グループ横断でのデータ活用・デジタル売上拡大</t>
         </is>
       </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>デジタル売上高1兆円目標（2026年度）</t>
         </is>
       </c>
-      <c r="I50" s="19" t="inlineStr">
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2420,17 +2666,22 @@
           <t>WAONアプリ等グループ共通基盤への統合</t>
         </is>
       </c>
-      <c r="G51" s="18" t="inlineStr">
+      <c r="G51" s="16" t="inlineStr">
+        <is>
+          <t>2025年2月</t>
+        </is>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>ポイント統合・顧客接点の一元化</t>
         </is>
       </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>独自アプリ終了→グループ統合完了</t>
         </is>
       </c>
-      <c r="I51" s="19" t="inlineStr">
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2451,17 +2702,22 @@
           <t>ウエルシアとのグループデータ連携</t>
         </is>
       </c>
-      <c r="G52" s="18" t="inlineStr">
+      <c r="G52" s="16" t="inlineStr">
+        <is>
+          <t>検討中</t>
+        </is>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
         <is>
           <t>食品×調剤のクロスユース促進</t>
         </is>
       </c>
-      <c r="H52" s="18" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>検討・推進中</t>
         </is>
       </c>
-      <c r="I52" s="19" t="inlineStr">
+      <c r="J52" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2482,17 +2738,22 @@
           <t>イオングループリテールメディア展開</t>
         </is>
       </c>
-      <c r="G53" s="18" t="inlineStr">
+      <c r="G53" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
         <is>
           <t>グループデータ活用での広告収益化</t>
         </is>
       </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>グループ全体で展開中</t>
         </is>
       </c>
-      <c r="I53" s="19" t="inlineStr">
+      <c r="J53" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2529,17 +2790,22 @@
           <t>AIワーク・MaIボード</t>
         </is>
       </c>
-      <c r="G54" s="18" t="inlineStr">
+      <c r="G54" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
         <is>
           <t>店舗業務効率化・AI活用推進</t>
         </is>
       </c>
-      <c r="H54" s="18" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>約350店導入</t>
         </is>
       </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2560,17 +2826,22 @@
           <t>生成AI内製化推進</t>
         </is>
       </c>
-      <c r="G55" s="18" t="inlineStr">
+      <c r="G55" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>内製DXスキル育成・コスト削減</t>
         </is>
       </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>グループ全体で推進中</t>
         </is>
       </c>
-      <c r="I55" s="19" t="inlineStr">
+      <c r="J55" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2591,17 +2862,22 @@
           <t>グループ顧客データ統合基盤</t>
         </is>
       </c>
-      <c r="G56" s="18" t="inlineStr">
+      <c r="G56" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
         <is>
           <t>デジタル売上高拡大・顧客データ活用</t>
         </is>
       </c>
-      <c r="H56" s="18" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>1兆円目標（2026年度）</t>
         </is>
       </c>
-      <c r="I56" s="19" t="inlineStr">
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2622,17 +2898,22 @@
           <t>iAEONアプリ（WAON統合）</t>
         </is>
       </c>
-      <c r="G57" s="18" t="inlineStr">
+      <c r="G57" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>決済・ポイント統合・顧客接点拡大</t>
         </is>
       </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>グループ共通アプリとして展開</t>
         </is>
       </c>
-      <c r="I57" s="19" t="inlineStr">
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2653,17 +2934,22 @@
           <t>ネットスーパー強化</t>
         </is>
       </c>
-      <c r="G58" s="18" t="inlineStr">
+      <c r="G58" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
         <is>
           <t>EC・即配送で利便性向上・顧客獲得</t>
         </is>
       </c>
-      <c r="H58" s="18" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>拡大中</t>
         </is>
       </c>
-      <c r="I58" s="19" t="inlineStr">
+      <c r="J58" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2684,17 +2970,22 @@
           <t>イオンメディアグループリテールメディア</t>
         </is>
       </c>
-      <c r="G59" s="18" t="inlineStr">
+      <c r="G59" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>グループデータ活用での広告収益化</t>
         </is>
       </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>グループ展開中</t>
         </is>
       </c>
-      <c r="I59" s="19" t="inlineStr">
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2731,17 +3022,22 @@
           <t>PPIHグループ共通デジタル基盤</t>
         </is>
       </c>
-      <c r="G60" s="18" t="inlineStr">
+      <c r="G60" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>グループデータ活用・DX推進</t>
         </is>
       </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>グループ展開中</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2762,17 +3058,22 @@
           <t>majicaアプリ（PPIH共通ポイント）</t>
         </is>
       </c>
-      <c r="G61" s="18" t="inlineStr">
+      <c r="G61" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>ポイント統合・顧客接点拡大</t>
         </is>
       </c>
-      <c r="H61" s="18" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>グループ共通アプリとして展開</t>
         </is>
       </c>
-      <c r="I61" s="19" t="inlineStr">
+      <c r="J61" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2809,17 +3110,22 @@
           <t>グループ内データ共有クラウドシステム</t>
         </is>
       </c>
-      <c r="G62" s="18" t="inlineStr">
+      <c r="G62" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>商品・販売データのリアルタイム共有</t>
         </is>
       </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>約1,300店舗に展開済み</t>
         </is>
       </c>
-      <c r="I62" s="19" t="inlineStr">
+      <c r="J62" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2840,17 +3146,22 @@
           <t>製造小売業DX（3つのコネクト戦略）</t>
         </is>
       </c>
-      <c r="G63" s="18" t="inlineStr">
+      <c r="G63" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>製造〜流通〜販売の一元管理</t>
         </is>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>推進中</t>
         </is>
       </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="J63" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2887,17 +3198,22 @@
           <t>RETAILSTUDIO®（売場・販促管理）</t>
         </is>
       </c>
-      <c r="G64" s="18" t="inlineStr">
+      <c r="G64" s="16" t="inlineStr">
+        <is>
+          <t>2023年1月</t>
+        </is>
+      </c>
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>売場・販促管理のデジタル化・効率化</t>
         </is>
       </c>
-      <c r="H64" s="18" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>2023年1月導入</t>
         </is>
       </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2918,17 +3234,22 @@
           <t>LINEミニアプリ（デジタル会員証）</t>
         </is>
       </c>
-      <c r="G65" s="18" t="inlineStr">
+      <c r="G65" s="16" t="inlineStr">
+        <is>
+          <t>2023年2月</t>
+        </is>
+      </c>
+      <c r="H65" s="18" t="inlineStr">
         <is>
           <t>デジタル会員証化・来店促進</t>
         </is>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="I65" s="18" t="inlineStr">
         <is>
           <t>2023年2月導入（静岡県西部スーパー初）</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="J65" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -2949,17 +3270,22 @@
           <t>スマートレシート</t>
         </is>
       </c>
-      <c r="G66" s="18" t="inlineStr">
+      <c r="G66" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>ペーパーレスレシート・購買履歴のデジタル管理</t>
         </is>
       </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="J66" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -2996,17 +3322,22 @@
           <t>（DX情報確認できていない）</t>
         </is>
       </c>
-      <c r="G67" s="18" t="inlineStr">
+      <c r="G67" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H67" s="18" t="inlineStr">
         <is>
           <t>地元密着・生鮮強みでの顧客囲い込みに注力</t>
         </is>
       </c>
-      <c r="H67" s="18" t="inlineStr">
+      <c r="I67" s="18" t="inlineStr">
         <is>
           <t>確認できていない</t>
         </is>
       </c>
-      <c r="I67" s="19" t="inlineStr">
+      <c r="J67" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -3043,17 +3374,22 @@
           <t>AIプライシング（価格最適化）</t>
         </is>
       </c>
-      <c r="G68" s="18" t="inlineStr">
+      <c r="G68" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H68" s="18" t="inlineStr">
         <is>
           <t>競争力強化・粗利管理の自動化</t>
         </is>
       </c>
-      <c r="H68" s="18" t="inlineStr">
+      <c r="I68" s="18" t="inlineStr">
         <is>
           <t>実装済み（詳細非公開）</t>
         </is>
       </c>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="J68" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -3074,17 +3410,22 @@
           <t>内製DXチームによる業務自動化基盤</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
+      <c r="G69" s="16" t="inlineStr">
+        <is>
+          <t>継続中</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
         <is>
           <t>現場業務の自動化・効率化</t>
         </is>
       </c>
-      <c r="H69" s="18" t="inlineStr">
+      <c r="I69" s="18" t="inlineStr">
         <is>
           <t>年間300万時間削減</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="J69" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -3105,17 +3446,22 @@
           <t>majicaアプリ（PPIH共通ポイント）</t>
         </is>
       </c>
-      <c r="G70" s="18" t="inlineStr">
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H70" s="18" t="inlineStr">
         <is>
           <t>ポイント統合・顧客接点拡大</t>
         </is>
       </c>
-      <c r="H70" s="18" t="inlineStr">
+      <c r="I70" s="18" t="inlineStr">
         <is>
           <t>グループ共通アプリとして展開</t>
         </is>
       </c>
-      <c r="I70" s="19" t="inlineStr">
+      <c r="J70" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -3136,17 +3482,22 @@
           <t>無人小型店舗「キャンパスドンキ」</t>
         </is>
       </c>
-      <c r="G71" s="18" t="inlineStr">
+      <c r="G71" s="16" t="inlineStr">
+        <is>
+          <t>実証中</t>
+        </is>
+      </c>
+      <c r="H71" s="18" t="inlineStr">
         <is>
           <t>無人化・新業態の実証</t>
         </is>
       </c>
-      <c r="H71" s="18" t="inlineStr">
+      <c r="I71" s="18" t="inlineStr">
         <is>
           <t>AIカメラ×重量センサーで実証中</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="J71" s="8" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
@@ -3183,17 +3534,22 @@
           <t>（DX情報確認できていない）</t>
         </is>
       </c>
-      <c r="G72" s="18" t="inlineStr">
+      <c r="G72" s="16" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H72" s="18" t="inlineStr">
         <is>
           <t>調達・製造コスト削減で価格競争力を確保</t>
         </is>
       </c>
-      <c r="H72" s="18" t="inlineStr">
+      <c r="I72" s="18" t="inlineStr">
         <is>
           <t>確認できていない</t>
         </is>
       </c>
-      <c r="I72" s="19" t="inlineStr">
+      <c r="J72" s="19" t="inlineStr">
         <is>
           <t>不明</t>
         </is>
@@ -3230,17 +3586,22 @@
           <t>生成AIナレッジ検索（NECと共同開発）</t>
         </is>
       </c>
-      <c r="G73" s="24" t="inlineStr">
+      <c r="G73" s="22" t="inlineStr">
+        <is>
+          <t>2026年2月（1,000店完了）</t>
+        </is>
+      </c>
+      <c r="H73" s="24" t="inlineStr">
         <is>
           <t>従業員の情報アクセス効率化・ナレッジ共有</t>
         </is>
       </c>
-      <c r="H73" s="24" t="inlineStr">
+      <c r="I73" s="24" t="inlineStr">
         <is>
           <t>1,000店舗展開完了（2026年2月）</t>
         </is>
       </c>
-      <c r="I73" s="25" t="inlineStr">
+      <c r="J73" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3261,17 +3622,22 @@
           <t>業界初データクリーンルーム「ツルハDCR」</t>
         </is>
       </c>
-      <c r="G74" s="24" t="inlineStr">
+      <c r="G74" s="22" t="inlineStr">
+        <is>
+          <t>2025年2月</t>
+        </is>
+      </c>
+      <c r="H74" s="24" t="inlineStr">
         <is>
           <t>リテールメディア強化・ファーストパーティデータ活用</t>
         </is>
       </c>
-      <c r="H74" s="24" t="inlineStr">
+      <c r="I74" s="24" t="inlineStr">
         <is>
           <t>2025年2月構築</t>
         </is>
       </c>
-      <c r="I74" s="25" t="inlineStr">
+      <c r="J74" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3292,17 +3658,22 @@
           <t>SmartDB（契約管理・内部統制）</t>
         </is>
       </c>
-      <c r="G75" s="24" t="inlineStr">
+      <c r="G75" s="22" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H75" s="24" t="inlineStr">
         <is>
           <t>契約管理のデジタル化・内部統制強化</t>
         </is>
       </c>
-      <c r="H75" s="24" t="inlineStr">
+      <c r="I75" s="24" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I75" s="25" t="inlineStr">
+      <c r="J75" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3323,17 +3694,22 @@
           <t>スマホアプリ（楽天ポイント連携・個別商品提案）</t>
         </is>
       </c>
-      <c r="G76" s="24" t="inlineStr">
+      <c r="G76" s="22" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="H76" s="24" t="inlineStr">
         <is>
           <t>顧客接点デジタル化・購買促進</t>
         </is>
       </c>
-      <c r="H76" s="24" t="inlineStr">
+      <c r="I76" s="24" t="inlineStr">
         <is>
           <t>実装済み</t>
         </is>
       </c>
-      <c r="I76" s="25" t="inlineStr">
+      <c r="J76" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3354,17 +3730,22 @@
           <t>データクリーンルーム活用リテールメディア</t>
         </is>
       </c>
-      <c r="G77" s="24" t="inlineStr">
+      <c r="G77" s="22" t="inlineStr">
+        <is>
+          <t>2025年〜継続中</t>
+        </is>
+      </c>
+      <c r="H77" s="24" t="inlineStr">
         <is>
           <t>広告収益化・購買データ提供</t>
         </is>
       </c>
-      <c r="H77" s="24" t="inlineStr">
+      <c r="I77" s="24" t="inlineStr">
         <is>
           <t>リテールAIアワード2024受賞</t>
         </is>
       </c>
-      <c r="I77" s="25" t="inlineStr">
+      <c r="J77" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3385,17 +3766,22 @@
           <t>生成AIナレッジ検索（画像・図表対応）</t>
         </is>
       </c>
-      <c r="G78" s="24" t="inlineStr">
+      <c r="G78" s="22" t="inlineStr">
+        <is>
+          <t>2026年2月（1,000店完了）</t>
+        </is>
+      </c>
+      <c r="H78" s="24" t="inlineStr">
         <is>
           <t>従業員の業務効率化・ナレッジ活用</t>
         </is>
       </c>
-      <c r="H78" s="24" t="inlineStr">
+      <c r="I78" s="24" t="inlineStr">
         <is>
           <t>1,000店舗展開完了（2026年2月）</t>
         </is>
       </c>
-      <c r="I78" s="25" t="inlineStr">
+      <c r="J78" s="25" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -3431,6 +3817,7 @@
     <mergeCell ref="A31:A35"/>
     <mergeCell ref="D41:D46"/>
     <mergeCell ref="D62:D63"/>
+    <mergeCell ref="A1:J1"/>
     <mergeCell ref="D37:D40"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="C60:C61"/>
@@ -3451,7 +3838,6 @@
     <mergeCell ref="D54:D59"/>
     <mergeCell ref="D3:D12"/>
     <mergeCell ref="D60:D61"/>
-    <mergeCell ref="A1:I1"/>
     <mergeCell ref="D73:D78"/>
     <mergeCell ref="A68:A71"/>
     <mergeCell ref="C68:C71"/>
@@ -4111,7 +4497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4334,74 +4720,166 @@
     <row r="19" ht="24" customHeight="1">
       <c r="A19" s="26" t="inlineStr">
         <is>
+          <t>■ 実装時期の表記ルール</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>表記</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>意味</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="38" t="inlineStr">
+        <is>
+          <t>YYYY年MM月</t>
+        </is>
+      </c>
+      <c r="B21" s="39" t="inlineStr">
+        <is>
+          <t>公表情報から確認できた具体的な導入・完了時期</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1">
+      <c r="A22" s="38" t="inlineStr">
+        <is>
+          <t>YYYY年頃</t>
+        </is>
+      </c>
+      <c r="B22" s="39" t="inlineStr">
+        <is>
+          <t>推定または概算の時期</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="38" t="inlineStr">
+        <is>
+          <t>YYYY年予定</t>
+        </is>
+      </c>
+      <c r="B23" s="39" t="inlineStr">
+        <is>
+          <t>今後の導入予定が公表されているもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="38" t="inlineStr">
+        <is>
+          <t>構築中 / 実証中 / 継続中</t>
+        </is>
+      </c>
+      <c r="B24" s="39" t="inlineStr">
+        <is>
+          <t>現在進行中の取り組み</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="38" t="inlineStr">
+        <is>
+          <t>検討中</t>
+        </is>
+      </c>
+      <c r="B25" s="39" t="inlineStr">
+        <is>
+          <t>導入・実施が検討段階にあるもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="38" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="B26" s="39" t="inlineStr">
+        <is>
+          <t>公表情報から時期が確認できないもの</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="26" t="inlineStr">
+        <is>
           <t>■ ツルハHD比較の意味</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="27" t="inlineStr">
+    <row r="29" ht="28" customHeight="1">
+      <c r="A29" s="27" t="inlineStr">
         <is>
           <t>ツルハHD比較</t>
         </is>
       </c>
-      <c r="B20" s="27" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>意味</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="40" t="inlineStr">
+    <row r="30" ht="28" customHeight="1">
+      <c r="A30" s="40" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="B21" s="39" t="inlineStr">
+      <c r="B30" s="39" t="inlineStr">
         <is>
           <t>ツルハHDが現時点で取り組んでいない施策。杏林堂にとって競合に遅れているリスク領域</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="28" customHeight="1">
-      <c r="A22" s="39" t="inlineStr">
+    <row r="31" ht="28" customHeight="1">
+      <c r="A31" s="39" t="inlineStr">
         <is>
           <t>同等</t>
         </is>
       </c>
-      <c r="B22" s="39" t="inlineStr">
+      <c r="B31" s="39" t="inlineStr">
         <is>
           <t>ツルハHDが同等レベルで取り組んでいる施策</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="28" customHeight="1">
-      <c r="A23" s="39" t="inlineStr">
-        <is>
-          <t>不明</t>
-        </is>
-      </c>
-      <c r="B23" s="39" t="inlineStr">
+    <row r="32" ht="28" customHeight="1">
+      <c r="A32" s="39" t="inlineStr">
+        <is>
+          <t>不明</t>
+        </is>
+      </c>
+      <c r="B32" s="39" t="inlineStr">
         <is>
           <t>ツルハHDの取り組み状況が確認できていない</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="28" customHeight="1">
-      <c r="A24" s="39" t="inlineStr">
+    <row r="33" ht="28" customHeight="1">
+      <c r="A33" s="39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="B24" s="39" t="inlineStr">
+      <c r="B33" s="39" t="inlineStr">
         <is>
           <t>ツルハHD自身の施策（参考行）</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A28:C28"/>
     <mergeCell ref="A19:C19"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
